--- a/recherche/Model_Benchmark_Detailed_v2.xlsx
+++ b/recherche/Model_Benchmark_Detailed_v2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\studying\3eme info(DSI33)\PFE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\studying\3eme info(DSI33)\PFE_Email_Analysis\recherche\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265E7997-6E8F-4D6B-BB20-F55E74045F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02C4E80-CF00-48FE-B039-B5B91CC29B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -333,7 +333,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -745,7 +745,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1181,7 +1181,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1995,7 +1995,7 @@
                         </a:solidFill>
                       </a:rPr>
                       <a:pPr/>
-                      <a:t>[VALUE]</a:t>
+                      <a:t>[VALEUR]</a:t>
                     </a:fld>
                     <a:r>
                       <a:rPr lang="en-US">
@@ -2012,7 +2012,7 @@
                         </a:solidFill>
                       </a:rPr>
                       <a:pPr/>
-                      <a:t>[PERCENTAGE]</a:t>
+                      <a:t>[POURCENTAGE]</a:t>
                     </a:fld>
                     <a:endParaRPr lang="en-US">
                       <a:solidFill>
@@ -2058,7 +2058,7 @@
                         </a:solidFill>
                       </a:rPr>
                       <a:pPr/>
-                      <a:t>[VALUE]</a:t>
+                      <a:t>[VALEUR]</a:t>
                     </a:fld>
                     <a:r>
                       <a:rPr lang="en-US">
@@ -2075,7 +2075,7 @@
                         </a:solidFill>
                       </a:rPr>
                       <a:pPr/>
-                      <a:t>[PERCENTAGE]</a:t>
+                      <a:t>[POURCENTAGE]</a:t>
                     </a:fld>
                     <a:endParaRPr lang="en-US">
                       <a:solidFill>
@@ -2121,7 +2121,7 @@
                         </a:solidFill>
                       </a:rPr>
                       <a:pPr/>
-                      <a:t>[VALUE]</a:t>
+                      <a:t>[VALEUR]</a:t>
                     </a:fld>
                     <a:r>
                       <a:rPr lang="en-US">
@@ -2138,7 +2138,7 @@
                         </a:solidFill>
                       </a:rPr>
                       <a:pPr/>
-                      <a:t>[PERCENTAGE]</a:t>
+                      <a:t>[POURCENTAGE]</a:t>
                     </a:fld>
                     <a:endParaRPr lang="en-US">
                       <a:solidFill>
@@ -2180,7 +2180,7 @@
                     <a:fld id="{68C209C4-01DB-4B73-9299-2E468865AE50}" type="VALUE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[VALUE]</a:t>
+                      <a:t>[VALEUR]</a:t>
                     </a:fld>
                     <a:r>
                       <a:rPr lang="en-US"/>
@@ -2189,7 +2189,7 @@
                     <a:fld id="{900FEBFF-62D9-41F5-B74C-1572D98CE8E0}" type="PERCENTAGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
-                      <a:t>[PERCENTAGE]</a:t>
+                      <a:t>[POURCENTAGE]</a:t>
                     </a:fld>
                     <a:endParaRPr lang="en-US"/>
                   </a:p>
@@ -2448,7 +2448,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2517,9 +2517,8 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="percentStacked"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -2536,15 +2535,17 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strRef>
               <c:f>Summary!$A$2:$A$11</c:f>
@@ -2622,6 +2623,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-63B2-43AB-B1EC-54611C634B6B}"/>
@@ -2643,15 +2645,17 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strRef>
               <c:f>Summary!$A$2:$A$11</c:f>
@@ -2729,6 +2733,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-63B2-43AB-B1EC-54611C634B6B}"/>
@@ -2743,11 +2748,10 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
+        <c:smooth val="0"/>
         <c:axId val="192310016"/>
         <c:axId val="192305856"/>
-      </c:barChart>
+      </c:lineChart>
       <c:catAx>
         <c:axId val="192310016"/>
         <c:scaling>
@@ -2820,7 +2824,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2973,7 +2977,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3437,7 +3441,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7576,7 +7580,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="20.5703125" customWidth="1"/>
@@ -8087,7 +8091,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="1"/>
     <col min="2" max="2" width="23.7109375" customWidth="1"/>
@@ -8260,7 +8264,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA0E1D4-74FD-447B-AB05-BE6E30B7BB39}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/recherche/Model_Benchmark_Detailed_v2.xlsx
+++ b/recherche/Model_Benchmark_Detailed_v2.xlsx
@@ -1,24 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\studying\3eme info(DSI33)\PFE_Email_Analysis\recherche\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02C4E80-CF00-48FE-B039-B5B91CC29B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D6926E-1326-4C5D-A26C-CB5543E5F610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Rankings" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -27,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="47">
   <si>
     <t>Model</t>
   </si>
@@ -256,12 +266,42 @@
   "confidence_score": 0.9
 }</t>
   </si>
+  <si>
+    <t>Iteration</t>
+  </si>
+  <si>
+    <t>Taux d'hallucination</t>
+  </si>
+  <si>
+    <t>LLM</t>
+  </si>
+  <si>
+    <t>Taux de confiance</t>
+  </si>
+  <si>
+    <t>llama3.1:latest + RAG</t>
+  </si>
+  <si>
+    <t>Nombre de type de ticket</t>
+  </si>
+  <si>
+    <t>238 types</t>
+  </si>
+  <si>
+    <t>8 types</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Score (/50)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,6 +322,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Geneva"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -300,10 +345,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -313,9 +359,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{06C5FDF6-7369-4C65-A5F6-B69E57C5052D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -331,6 +380,1720 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>qwen3:4b</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Both_Match_Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$M$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-92E5-4FD6-95C8-B2F514D71FD3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>phi3:mini</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Both_Match_Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$M$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-92E5-4FD6-95C8-B2F514D71FD3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>qwen2.5:3b</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Both_Match_Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$M$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>33</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-92E5-4FD6-95C8-B2F514D71FD3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>gemma:2b</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Both_Match_Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$M$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>31</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-92E5-4FD6-95C8-B2F514D71FD3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>qwen3:1.7b</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Both_Match_Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$M$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>42</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-92E5-4FD6-95C8-B2F514D71FD3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>qwen2.5:1.5b</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Both_Match_Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$M$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-92E5-4FD6-95C8-B2F514D71FD3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>qwen3:8b</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Both_Match_Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$M$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-92E5-4FD6-95C8-B2F514D71FD3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>llama3:8b</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Both_Match_Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$M$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-92E5-4FD6-95C8-B2F514D71FD3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>llama3.1:latest</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Both_Match_Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$M$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>46</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-92E5-4FD6-95C8-B2F514D71FD3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>gemma:latest</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Both_Match_Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$M$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-92E5-4FD6-95C8-B2F514D71FD3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1517783311"/>
+        <c:axId val="1517780399"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1517783311"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1517780399"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1517780399"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1517783311"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Taux d'hallucination</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$K$2:$K$3</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>238 types</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8 types</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$L$2:$L$3</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D116-482C-94A0-641485ECEC4F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="724703823"/>
+        <c:axId val="724704239"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="724703823"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="724704239"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="724704239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="724703823"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$J$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Score (/50)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$I$34:$I$43</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>llama3.1:latest</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>qwen3:1.7b</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>qwen2.5:3b</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gemma:2b</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>qwen3:4b</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>qwen3:8b</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>phi3:mini</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>llama3:8b</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>qwen2.5:1.5b</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>gemma:latest</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$J$34:$J$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A048-4F01-99B6-B5E61109D6A0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1254392335"/>
+        <c:axId val="1254392751"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1254392335"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1254392751"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1254392751"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1254392335"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mean_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$A$2:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>qwen3:4b</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>phi3:mini</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>qwen2.5:3b</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gemma:2b</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>qwen3:1.7b</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>qwen2.5:1.5b</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>qwen3:8b</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>llama3:8b</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>llama3.1:latest</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>gemma:latest</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$C$2:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>126.651</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.68</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.7250000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.76</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.72599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>26.782</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.7969999999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.8550000000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14.847</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4301-4DC7-8600-C5A161425D99}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="2064323551"/>
+        <c:axId val="2064316895"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2064323551"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2064316895"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2064316895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2064323551"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -496,31 +2259,31 @@
                   <c:v>qwen3:4b</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>phi3:mini</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>qwen2.5:3b</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gemma:2b</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>qwen3:1.7b</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>qwen2.5:1.5b</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>qwen3:8b</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>llama3:8b</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>llama3.1:latest</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>gemma:latest</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>qwen3:1.7b</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>llama3.1:latest</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>llama3:8b</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>phi3:mini</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>qwen2.5:3b</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>gemma:2b</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>qwen2.5:1.5b</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -535,31 +2298,31 @@
                   <c:v>92</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>87.82</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83.42</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>82.46</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>73.86</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>59.8</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>37.96</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>33.18</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>82.46</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>37.96</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>90</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>87.82</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>83.42</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>73.86</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -742,7 +2505,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -932,31 +2695,31 @@
                   <c:v>qwen3:4b</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>phi3:mini</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>qwen2.5:3b</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gemma:2b</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>qwen3:1.7b</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>qwen2.5:1.5b</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>qwen3:8b</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>llama3:8b</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>llama3.1:latest</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>gemma:latest</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>qwen3:1.7b</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>llama3.1:latest</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>llama3:8b</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>phi3:mini</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>qwen2.5:3b</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>gemma:2b</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>qwen2.5:1.5b</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -971,31 +2734,31 @@
                   <c:v>3659.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>4590.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4716.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3156.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2595.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2322.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>5464.6</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>5360.9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5405.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>5278.4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2595.6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5405.4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5360.9</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4590.8</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4716.5</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3156.5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2322.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1178,7 +2941,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -2267,31 +4030,31 @@
                   <c:v>qwen3:4b</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>phi3:mini</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>qwen2.5:3b</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gemma:2b</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>qwen3:1.7b</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>qwen2.5:1.5b</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>qwen3:8b</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>llama3:8b</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>llama3.1:latest</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>gemma:latest</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>qwen3:1.7b</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>llama3.1:latest</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>llama3:8b</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>phi3:mini</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>qwen2.5:3b</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>gemma:2b</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>qwen2.5:1.5b</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2306,31 +4069,31 @@
                   <c:v>6332.5640000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>134.005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>86.254999999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>54.503</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>337.98500000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>36.28</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>1339.087</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>239.85900000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>292.74299999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>742.35500000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>337.98500000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>292.74299999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>239.85900000000001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>134.005</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>86.254999999999995</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>54.503</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>36.28</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2445,7 +4208,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -2555,31 +4318,31 @@
                   <c:v>qwen3:4b</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>phi3:mini</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>qwen2.5:3b</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gemma:2b</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>qwen3:1.7b</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>qwen2.5:1.5b</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>qwen3:8b</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>llama3:8b</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>llama3.1:latest</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>gemma:latest</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>qwen3:1.7b</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>llama3.1:latest</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>llama3:8b</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>phi3:mini</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>qwen2.5:3b</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>gemma:2b</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>qwen2.5:1.5b</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2665,31 +4428,31 @@
                   <c:v>qwen3:4b</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>phi3:mini</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>qwen2.5:3b</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gemma:2b</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>qwen3:1.7b</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>qwen2.5:1.5b</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>qwen3:8b</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>llama3:8b</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>llama3.1:latest</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>gemma:latest</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>qwen3:1.7b</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>llama3.1:latest</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>llama3:8b</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>phi3:mini</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>qwen2.5:3b</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>gemma:2b</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>qwen2.5:1.5b</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2704,31 +4467,31 @@
                   <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>11</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>42</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2974,7 +4737,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -3189,31 +4952,31 @@
                   <c:v>qwen3:4b</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>phi3:mini</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>qwen2.5:3b</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gemma:2b</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>qwen3:1.7b</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>qwen2.5:1.5b</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>qwen3:8b</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>llama3:8b</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>llama3.1:latest</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>gemma:latest</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>qwen3:1.7b</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>llama3.1:latest</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>llama3:8b</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>phi3:mini</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>qwen2.5:3b</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>gemma:2b</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>qwen2.5:1.5b</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3228,31 +4991,31 @@
                   <c:v>126.651</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>2.68</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.7250000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.76</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.72599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>26.782</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>4.7969999999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.8550000000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>14.847</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.76</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.8550000000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4.7969999999999997</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.68</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.7250000000000001</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.0900000000000001</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.72599999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3438,7 +5201,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -3535,31 +5298,31 @@
                   <c:v>qwen3:4b</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>phi3:mini</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>qwen2.5:3b</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>gemma:2b</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>qwen3:1.7b</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>qwen2.5:1.5b</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>qwen3:8b</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>llama3:8b</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>llama3.1:latest</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>gemma:latest</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>qwen3:1.7b</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>llama3.1:latest</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>llama3:8b</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>phi3:mini</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>qwen2.5:3b</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>gemma:2b</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>qwen2.5:1.5b</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3574,31 +5337,31 @@
                   <c:v>8.0000000000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.373</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.91700000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.14799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.3779999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>3.6999999999999998E-2</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>0.20799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.17100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>6.7000000000000004E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.14799999999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.17100000000000001</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.20799999999999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.373</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.57999999999999996</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.91700000000000004</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.3779999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3802,7 +5565,362 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$Q$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Taux de confiance</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$P$2:$P$3</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>llama3.1:latest</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>llama3.1:latest + RAG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$Q$2:$Q$3</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.92</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5445-414A-BF49-EF439FCA921A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1622920031"/>
+        <c:axId val="1622920863"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1622920031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1622920863"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1622920863"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1622920031"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -4042,6 +6160,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -4545,7 +6783,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5048,7 +7286,2019 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="257">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5544,7 +9794,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6049,7 +10299,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="222">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6545,7 +10795,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7061,7 +11311,587 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B809C1A-BC40-4B1C-9496-4C685D658168}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>885825</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Graphique 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B69C048-7A77-45E0-84DF-E14C60999F3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -7294,6 +12124,119 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFC28995-40E1-4DFE-AE15-E176AE3EFAAD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>376237</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>804862</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D427531-2C8D-4AAB-BAB2-4DB3962F176F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1171575</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Graphique 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1509CFD-991D-4DB0-B75E-5A64F88C37BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -7580,7 +12523,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="20.5703125" customWidth="1"/>
@@ -7595,7 +12538,7 @@
     <col min="14" max="14" width="59.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7639,7 +12582,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="30" customHeight="1">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -7683,415 +12626,416 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="26.25" customHeight="1">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>1339.087</v>
+        <v>134.005</v>
       </c>
       <c r="C3">
-        <v>26.782</v>
+        <v>2.68</v>
       </c>
       <c r="D3">
-        <v>17.440999999999999</v>
+        <v>2.1579999999999999</v>
       </c>
       <c r="E3">
-        <v>13.275</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="F3">
-        <v>93.960999999999999</v>
+        <v>32.826000000000001</v>
       </c>
       <c r="G3">
-        <v>18.434000000000001</v>
+        <v>4.3659999999999997</v>
       </c>
       <c r="H3">
-        <v>46.930999999999997</v>
+        <v>2.585</v>
       </c>
       <c r="I3">
-        <v>3.6999999999999998E-2</v>
+        <v>0.373</v>
       </c>
       <c r="J3">
-        <v>59.8</v>
+        <v>90</v>
       </c>
       <c r="K3">
-        <v>5464.6</v>
+        <v>4590.8</v>
       </c>
       <c r="L3" s="4">
         <v>50</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="31.5" customHeight="1">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4">
-        <v>742.35500000000002</v>
+        <v>86.254999999999995</v>
       </c>
       <c r="C4">
-        <v>14.847</v>
+        <v>1.7250000000000001</v>
       </c>
       <c r="D4">
-        <v>15.180999999999999</v>
+        <v>1.5820000000000001</v>
       </c>
       <c r="E4">
-        <v>11.71</v>
+        <v>1.476</v>
       </c>
       <c r="F4">
-        <v>21.672000000000001</v>
+        <v>5.2759999999999998</v>
       </c>
       <c r="G4">
-        <v>1.601</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="H4">
-        <v>16.614999999999998</v>
+        <v>1.9259999999999999</v>
       </c>
       <c r="I4">
-        <v>6.7000000000000004E-2</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="J4">
-        <v>33.18</v>
+        <v>87.82</v>
       </c>
       <c r="K4">
-        <v>5278.4</v>
+        <v>4716.5</v>
       </c>
       <c r="L4" s="4">
         <v>50</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B5">
-        <v>337.98500000000001</v>
+        <v>54.503</v>
       </c>
       <c r="C5">
-        <v>6.76</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="D5">
-        <v>6.39</v>
+        <v>0.95899999999999996</v>
       </c>
       <c r="E5">
-        <v>3.38</v>
+        <v>0.86199999999999999</v>
       </c>
       <c r="F5">
-        <v>11.367000000000001</v>
+        <v>6.2809999999999997</v>
       </c>
       <c r="G5">
-        <v>2.25</v>
+        <v>0.754</v>
       </c>
       <c r="H5">
-        <v>9.8989999999999991</v>
+        <v>1.099</v>
       </c>
       <c r="I5">
-        <v>0.14799999999999999</v>
+        <v>0.91700000000000004</v>
       </c>
       <c r="J5">
-        <v>82.46</v>
+        <v>83.42</v>
       </c>
       <c r="K5">
-        <v>2595.6</v>
+        <v>3156.5</v>
       </c>
       <c r="L5" s="4">
         <v>50</v>
       </c>
       <c r="M5">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="27.75" customHeight="1">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>292.74299999999999</v>
+        <v>337.98500000000001</v>
       </c>
       <c r="C6">
-        <v>5.8550000000000004</v>
+        <v>6.76</v>
       </c>
       <c r="D6">
-        <v>5.5650000000000004</v>
+        <v>6.39</v>
       </c>
       <c r="E6">
-        <v>5.0149999999999997</v>
+        <v>3.38</v>
       </c>
       <c r="F6">
-        <v>13.221</v>
+        <v>11.367000000000001</v>
       </c>
       <c r="G6">
-        <v>1.151</v>
+        <v>2.25</v>
       </c>
       <c r="H6">
-        <v>6.4039999999999999</v>
+        <v>9.8989999999999991</v>
       </c>
       <c r="I6">
-        <v>0.17100000000000001</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="J6">
-        <v>35</v>
+        <v>82.46</v>
       </c>
       <c r="K6">
-        <v>5405.4</v>
+        <v>2595.6</v>
       </c>
       <c r="L6" s="4">
         <v>50</v>
       </c>
       <c r="M6">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="31.5" customHeight="1">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>239.85900000000001</v>
+        <v>36.28</v>
       </c>
       <c r="C7">
-        <v>4.7969999999999997</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="D7">
-        <v>4.2880000000000003</v>
+        <v>0.64100000000000001</v>
       </c>
       <c r="E7">
-        <v>3.278</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="F7">
-        <v>25.821999999999999</v>
+        <v>3.4249999999999998</v>
       </c>
       <c r="G7">
-        <v>3.069</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="H7">
-        <v>5.0179999999999998</v>
+        <v>0.81899999999999995</v>
       </c>
       <c r="I7">
-        <v>0.20799999999999999</v>
+        <v>1.3779999999999999</v>
       </c>
       <c r="J7">
-        <v>37.96</v>
+        <v>73.86</v>
       </c>
       <c r="K7">
-        <v>5360.9</v>
+        <v>2322.6</v>
       </c>
       <c r="L7" s="4">
         <v>50</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="27" customHeight="1">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>134.005</v>
+        <v>1339.087</v>
       </c>
       <c r="C8">
-        <v>2.68</v>
+        <v>26.782</v>
       </c>
       <c r="D8">
-        <v>2.1579999999999999</v>
+        <v>17.440999999999999</v>
       </c>
       <c r="E8">
-        <v>1.3140000000000001</v>
+        <v>13.275</v>
       </c>
       <c r="F8">
-        <v>32.826000000000001</v>
+        <v>93.960999999999999</v>
       </c>
       <c r="G8">
-        <v>4.3659999999999997</v>
+        <v>18.434000000000001</v>
       </c>
       <c r="H8">
-        <v>2.585</v>
+        <v>46.930999999999997</v>
       </c>
       <c r="I8">
-        <v>0.373</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="J8">
-        <v>90</v>
+        <v>59.8</v>
       </c>
       <c r="K8">
-        <v>4590.8</v>
+        <v>5464.6</v>
       </c>
       <c r="L8" s="4">
         <v>50</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="30.75" customHeight="1">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B9">
-        <v>86.254999999999995</v>
+        <v>239.85900000000001</v>
       </c>
       <c r="C9">
-        <v>1.7250000000000001</v>
+        <v>4.7969999999999997</v>
       </c>
       <c r="D9">
-        <v>1.5820000000000001</v>
+        <v>4.2880000000000003</v>
       </c>
       <c r="E9">
-        <v>1.476</v>
+        <v>3.278</v>
       </c>
       <c r="F9">
-        <v>5.2759999999999998</v>
+        <v>25.821999999999999</v>
       </c>
       <c r="G9">
-        <v>0.54500000000000004</v>
+        <v>3.069</v>
       </c>
       <c r="H9">
-        <v>1.9259999999999999</v>
+        <v>5.0179999999999998</v>
       </c>
       <c r="I9">
-        <v>0.57999999999999996</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="J9">
-        <v>87.82</v>
+        <v>37.96</v>
       </c>
       <c r="K9">
-        <v>4716.5</v>
+        <v>5360.9</v>
       </c>
       <c r="L9" s="4">
         <v>50</v>
       </c>
       <c r="M9">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="N9" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="29.25" customHeight="1">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>292.74299999999999</v>
+      </c>
+      <c r="C10">
+        <v>5.8550000000000004</v>
+      </c>
+      <c r="D10">
+        <v>5.5650000000000004</v>
+      </c>
+      <c r="E10">
+        <v>5.0149999999999997</v>
+      </c>
+      <c r="F10">
+        <v>13.221</v>
+      </c>
+      <c r="G10">
+        <v>1.151</v>
+      </c>
+      <c r="H10">
+        <v>6.4039999999999999</v>
+      </c>
+      <c r="I10">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="J10">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10">
-        <v>54.503</v>
-      </c>
-      <c r="C10">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="D10">
-        <v>0.95899999999999996</v>
-      </c>
-      <c r="E10">
-        <v>0.86199999999999999</v>
-      </c>
-      <c r="F10">
-        <v>6.2809999999999997</v>
-      </c>
-      <c r="G10">
-        <v>0.754</v>
-      </c>
-      <c r="H10">
-        <v>1.099</v>
-      </c>
-      <c r="I10">
-        <v>0.91700000000000004</v>
-      </c>
-      <c r="J10">
-        <v>83.42</v>
-      </c>
       <c r="K10">
-        <v>3156.5</v>
+        <v>5405.4</v>
       </c>
       <c r="L10" s="4">
         <v>50</v>
       </c>
       <c r="M10">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="28.5" customHeight="1">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B11">
-        <v>36.28</v>
+        <v>742.35500000000002</v>
       </c>
       <c r="C11">
-        <v>0.72599999999999998</v>
+        <v>14.847</v>
       </c>
       <c r="D11">
-        <v>0.64100000000000001</v>
+        <v>15.180999999999999</v>
       </c>
       <c r="E11">
-        <v>0.55100000000000005</v>
+        <v>11.71</v>
       </c>
       <c r="F11">
-        <v>3.4249999999999998</v>
+        <v>21.672000000000001</v>
       </c>
       <c r="G11">
-        <v>0.40300000000000002</v>
+        <v>1.601</v>
       </c>
       <c r="H11">
-        <v>0.81899999999999995</v>
+        <v>16.614999999999998</v>
       </c>
       <c r="I11">
-        <v>1.3779999999999999</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="J11">
-        <v>73.86</v>
+        <v>33.18</v>
       </c>
       <c r="K11">
-        <v>2322.6</v>
+        <v>5278.4</v>
       </c>
       <c r="L11" s="4">
         <v>50</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N11">
-    <sortCondition descending="1" ref="C1:C11"/>
+    <sortCondition descending="1" ref="J1:J11"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="1"/>
     <col min="2" max="2" width="23.7109375" customWidth="1"/>
@@ -8099,7 +13043,7 @@
     <col min="4" max="4" width="36.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8113,7 +13057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -8127,7 +13071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -8141,7 +13085,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -8155,7 +13099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -8169,7 +13113,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -8183,7 +13127,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -8197,7 +13141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -8211,7 +13155,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -8225,7 +13169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -8239,7 +13183,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -8264,9 +13208,453 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA0E1D4-74FD-447B-AB05-BE6E30B7BB39}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC4BA7A-9966-45ED-A77B-359A666B19E4}">
+  <dimension ref="B1:Q51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="24.85546875" customWidth="1"/>
+    <col min="12" max="12" width="21.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" customWidth="1"/>
+    <col min="16" max="16" width="19.42578125" customWidth="1"/>
+    <col min="17" max="17" width="18.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:17">
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="2:17">
+      <c r="B2" s="5">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="5">
+        <v>1</v>
+      </c>
+      <c r="P2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17">
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="K3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="P3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17">
+      <c r="B4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17">
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17">
+      <c r="B6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17">
+      <c r="B7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17">
+      <c r="B8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17">
+      <c r="B9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17">
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>9</v>
+      </c>
+      <c r="F10" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17">
+      <c r="B11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17">
+      <c r="B12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="2:17">
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17">
+      <c r="B14" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17">
+      <c r="B15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17">
+      <c r="B16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
+      <c r="B33" s="5">
+        <v>1</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
+      <c r="B34" s="5">
+        <v>1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>19</v>
+      </c>
+      <c r="J34">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10">
+      <c r="B35" s="5">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10">
+      <c r="B36" s="5">
+        <v>1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10">
+      <c r="B37" s="5">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10">
+      <c r="B38" s="5">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10">
+      <c r="B39" s="5">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10">
+      <c r="B40" s="5">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10">
+      <c r="B41" s="5">
+        <v>1</v>
+      </c>
+      <c r="I41" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
+      <c r="B42" s="5">
+        <v>1</v>
+      </c>
+      <c r="I42" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10">
+      <c r="B43" s="5">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
+      <c r="B44" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10">
+      <c r="B45" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10">
+      <c r="B46" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10">
+      <c r="B47" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10">
+      <c r="B48" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>